--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,43 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00196</v>
+        <v>0.01245</v>
+      </c>
+      <c r="E2">
+        <v>-0.178</v>
       </c>
       <c r="G2">
-        <v>0.1461637156787272</v>
+        <v>0.07536332179930796</v>
       </c>
       <c r="H2">
-        <v>0.1461637156787272</v>
+        <v>0.07536332179930796</v>
       </c>
       <c r="I2">
-        <v>0.1017502706829581</v>
+        <v>0.006412217440843681</v>
       </c>
       <c r="J2">
-        <v>0.09738220350717453</v>
+        <v>0.006079275381415259</v>
       </c>
       <c r="K2">
-        <v>27.76</v>
+        <v>-4.696</v>
       </c>
       <c r="L2">
-        <v>0.07123428278162688</v>
+        <v>-0.01083275663206459</v>
       </c>
       <c r="M2">
-        <v>40.16</v>
+        <v>10.08</v>
       </c>
       <c r="N2">
-        <v>0.1100877192982456</v>
+        <v>0.02868525896414343</v>
       </c>
       <c r="O2">
-        <v>1.446685878962536</v>
+        <v>-2.146507666098808</v>
       </c>
       <c r="P2">
-        <v>40.16</v>
+        <v>10.08</v>
       </c>
       <c r="Q2">
-        <v>0.1100877192982456</v>
+        <v>0.02868525896414343</v>
       </c>
       <c r="R2">
-        <v>1.446685878962536</v>
+        <v>-2.146507666098808</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>58.5</v>
+        <v>100.75</v>
       </c>
       <c r="V2">
-        <v>0.1603618421052632</v>
+        <v>0.2867103016505407</v>
       </c>
       <c r="W2">
-        <v>0.1235897435897436</v>
+        <v>-0.07258523505695386</v>
       </c>
       <c r="X2">
-        <v>0.0528688789998222</v>
+        <v>0.08803084284500959</v>
       </c>
       <c r="Y2">
-        <v>0.07072086458992141</v>
+        <v>-0.1606160779019634</v>
       </c>
       <c r="Z2">
-        <v>1.509326700330836</v>
+        <v>1.239398218031192</v>
       </c>
       <c r="AA2">
-        <v>0.1278648974668275</v>
+        <v>-0.0261756277887779</v>
       </c>
       <c r="AB2">
-        <v>0.05067212097004738</v>
+        <v>0.08681079478660299</v>
       </c>
       <c r="AC2">
-        <v>0.08407141958799996</v>
+        <v>-0.1156205832046331</v>
       </c>
       <c r="AD2">
-        <v>49.74</v>
+        <v>38.76</v>
       </c>
       <c r="AE2">
-        <v>0.01459757425615745</v>
+        <v>0.04651869697132015</v>
       </c>
       <c r="AF2">
-        <v>49.75459757425616</v>
+        <v>38.80651869697132</v>
       </c>
       <c r="AG2">
-        <v>-8.745402425743841</v>
+        <v>-61.94348130302868</v>
       </c>
       <c r="AH2">
-        <v>0.1200194084576374</v>
+        <v>0.09945123117512011</v>
       </c>
       <c r="AI2">
-        <v>0.1447387116430011</v>
+        <v>0.09041456037243817</v>
       </c>
       <c r="AJ2">
-        <v>-0.02456197022963582</v>
+        <v>-0.213999261726341</v>
       </c>
       <c r="AK2">
-        <v>-0.03065823478433955</v>
+        <v>-0.188589593376823</v>
       </c>
       <c r="AL2">
-        <v>2.599</v>
+        <v>1.62</v>
       </c>
       <c r="AM2">
-        <v>2.599</v>
+        <v>1.62</v>
       </c>
       <c r="AN2">
-        <v>1.140171919770774</v>
+        <v>5.010989010989012</v>
       </c>
       <c r="AO2">
-        <v>15.25202000769527</v>
+        <v>1.691358024691359</v>
       </c>
       <c r="AP2">
-        <v>-0.2004676773809476</v>
+        <v>-8.008207020430341</v>
       </c>
       <c r="AQ2">
-        <v>15.25202000769527</v>
+        <v>1.691358024691359</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dubai Islamic Insurance &amp; Reinsurance Co. (Aman) (P.J.S.C) (DFM:AMAN)</t>
+          <t>Islamic Arab Insurance Co. (Salama) PJSC (DFM:SALAMA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,109 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.08710000000000001</v>
+        <v>0.011</v>
+      </c>
+      <c r="E3">
+        <v>-0.178</v>
       </c>
       <c r="G3">
-        <v>0.144141689373297</v>
+        <v>0.07951219512195122</v>
       </c>
       <c r="H3">
-        <v>0.144141689373297</v>
+        <v>0.07951219512195122</v>
       </c>
       <c r="I3">
-        <v>0.2</v>
+        <v>0.04843754273466213</v>
       </c>
       <c r="J3">
-        <v>0.2</v>
+        <v>0.03837743770515538</v>
       </c>
       <c r="K3">
-        <v>7.34</v>
+        <v>4.94</v>
       </c>
       <c r="L3">
-        <v>0.2</v>
+        <v>0.02409756097560976</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>6.46</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.03760186263096624</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>1.307692307692307</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>6.46</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.03760186263096624</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>1.307692307692307</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>17.7</v>
+        <v>48.3</v>
       </c>
       <c r="V3">
-        <v>0.2618343195266272</v>
+        <v>0.2811408614668218</v>
       </c>
       <c r="W3">
-        <v>0.3511961722488038</v>
+        <v>0.02364767831498325</v>
       </c>
       <c r="X3">
-        <v>0.0528688789998222</v>
+        <v>0.08633540778312301</v>
       </c>
       <c r="Y3">
-        <v>0.2983272932489817</v>
+        <v>-0.06268772946813977</v>
       </c>
       <c r="Z3">
-        <v>13.64312267657994</v>
+        <v>1.039835759489621</v>
       </c>
       <c r="AA3">
-        <v>2.728624535315987</v>
+        <v>0.03990623208340587</v>
       </c>
       <c r="AB3">
-        <v>0.05073284679373166</v>
+        <v>0.08587586696743588</v>
       </c>
       <c r="AC3">
-        <v>2.677891688522256</v>
+        <v>-0.04596963488403001</v>
       </c>
       <c r="AD3">
-        <v>4.14</v>
+        <v>2.38</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>0.04651869697132015</v>
       </c>
       <c r="AF3">
-        <v>4.14</v>
+        <v>2.42651869697132</v>
       </c>
       <c r="AG3">
-        <v>-13.56</v>
+        <v>-45.87348130302868</v>
       </c>
       <c r="AH3">
-        <v>0.05770839141343741</v>
+        <v>0.0139273786511898</v>
       </c>
       <c r="AI3">
-        <v>0.1508746355685131</v>
+        <v>0.01078805074220887</v>
       </c>
       <c r="AJ3">
-        <v>-0.2509252405625463</v>
+        <v>-0.3642876955363015</v>
       </c>
       <c r="AK3">
-        <v>-1.392197125256673</v>
+        <v>-0.2597202370371765</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AN3">
-        <v>0.5587044534412955</v>
+        <v>0.2214159456693646</v>
+      </c>
+      <c r="AO3">
+        <v>17.41197183098592</v>
       </c>
       <c r="AP3">
-        <v>-1.82995951417004</v>
+        <v>-4.267697581452105</v>
+      </c>
+      <c r="AQ3">
+        <v>17.41197183098592</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dar Al Takaful PJSC (DFM:DARTAKAFUL)</t>
+          <t>Al Fujairah National Insurance Company P.J.S.C (ADX:AFNIC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -841,43 +856,43 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.296</v>
+        <v>0.0139</v>
       </c>
       <c r="G4">
-        <v>0.01980676328502416</v>
+        <v>0.1106589147286822</v>
       </c>
       <c r="H4">
-        <v>0.01980676328502416</v>
+        <v>0.1106589147286822</v>
       </c>
       <c r="I4">
-        <v>0.07315389924085576</v>
+        <v>-0.02228682170542635</v>
       </c>
       <c r="J4">
-        <v>0.07315389924085576</v>
+        <v>-0.02228682170542635</v>
       </c>
       <c r="K4">
-        <v>4.82</v>
+        <v>-0.756</v>
       </c>
       <c r="L4">
-        <v>0.03326432022084196</v>
+        <v>-0.01465116279069767</v>
       </c>
       <c r="M4">
-        <v>3.76</v>
+        <v>3.62</v>
       </c>
       <c r="N4">
-        <v>0.07372549019607842</v>
+        <v>0.04756898817345599</v>
       </c>
       <c r="O4">
-        <v>0.7800829875518671</v>
+        <v>-4.788359788359789</v>
       </c>
       <c r="P4">
-        <v>3.76</v>
+        <v>3.62</v>
       </c>
       <c r="Q4">
-        <v>0.07372549019607842</v>
+        <v>0.04756898817345599</v>
       </c>
       <c r="R4">
-        <v>0.7800829875518671</v>
+        <v>-4.788359788359789</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -886,73 +901,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>15.6</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="V4">
-        <v>0.3058823529411764</v>
+        <v>0.1110381077529566</v>
       </c>
       <c r="W4">
-        <v>0.1235897435897436</v>
+        <v>-0.008729792147806005</v>
       </c>
       <c r="X4">
-        <v>0.06229892087371915</v>
+        <v>0.08972627790689615</v>
       </c>
       <c r="Y4">
-        <v>0.06129082271602445</v>
+        <v>-0.09845607005470215</v>
       </c>
       <c r="Z4">
-        <v>1.74788902291918</v>
+        <v>0.5987468090044095</v>
       </c>
       <c r="AA4">
-        <v>0.1278648974668275</v>
+        <v>-0.01334416337897424</v>
       </c>
       <c r="AB4">
-        <v>0.04379347787882753</v>
+        <v>0.0877457226057701</v>
       </c>
       <c r="AC4">
-        <v>0.08407141958799996</v>
+        <v>-0.1010898859847443</v>
       </c>
       <c r="AD4">
-        <v>32.2</v>
+        <v>6.58</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>32.2</v>
+        <v>6.58</v>
       </c>
       <c r="AG4">
-        <v>16.6</v>
+        <v>-1.869999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.3870192307692308</v>
+        <v>0.07958393807450412</v>
       </c>
       <c r="AI4">
-        <v>0.4472222222222222</v>
+        <v>0.07504562043795621</v>
       </c>
       <c r="AJ4">
-        <v>0.2455621301775148</v>
+        <v>-0.02519197090125285</v>
       </c>
       <c r="AK4">
-        <v>0.2943262411347518</v>
+        <v>-0.02360217089486305</v>
       </c>
       <c r="AL4">
-        <v>1.62</v>
+        <v>0.042</v>
       </c>
       <c r="AM4">
-        <v>1.62</v>
+        <v>0.042</v>
       </c>
       <c r="AN4">
-        <v>2.35036496350365</v>
+        <v>13.31983805668016</v>
       </c>
       <c r="AO4">
-        <v>6.54320987654321</v>
+        <v>-27.38095238095238</v>
       </c>
       <c r="AP4">
-        <v>1.211678832116788</v>
+        <v>-3.785425101214573</v>
       </c>
       <c r="AQ4">
-        <v>6.54320987654321</v>
+        <v>-27.38095238095238</v>
       </c>
     </row>
     <row r="5">
@@ -963,7 +978,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Islamic Arab Insurance Co. (Salama) PJSC (DFM:SALAMA)</t>
+          <t>Dar Al Takaful PJSC (DFM:DARTAKAFUL)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -972,118 +987,237 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.00196</v>
+        <v>0.213</v>
       </c>
       <c r="G5">
-        <v>0.2345026429601153</v>
+        <v>0.05716363636363637</v>
       </c>
       <c r="H5">
-        <v>0.2345026429601153</v>
+        <v>0.05716363636363637</v>
       </c>
       <c r="I5">
-        <v>0.1043348413510272</v>
+        <v>-0.016</v>
       </c>
       <c r="J5">
-        <v>0.09089777844975858</v>
+        <v>-0.016</v>
       </c>
       <c r="K5">
-        <v>15.6</v>
+        <v>-5.66</v>
       </c>
       <c r="L5">
-        <v>0.07496395963479097</v>
+        <v>-0.04116363636363637</v>
       </c>
       <c r="M5">
-        <v>36.4</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.1478472786352559</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>2.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>36.4</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.1478472786352559</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>2.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>25.2</v>
+        <v>15</v>
       </c>
       <c r="V5">
-        <v>0.1023558082859464</v>
+        <v>0.3036437246963563</v>
       </c>
       <c r="W5">
-        <v>0.06718346253229975</v>
+        <v>-0.1422110552763819</v>
       </c>
       <c r="X5">
-        <v>0.05275713337930942</v>
+        <v>0.1139491992194216</v>
       </c>
       <c r="Y5">
-        <v>0.01442632915299032</v>
+        <v>-0.2561602544958035</v>
       </c>
       <c r="Z5">
-        <v>1.205645752920767</v>
+        <v>2.437943262411348</v>
       </c>
       <c r="AA5">
-        <v>0.1095905205378842</v>
+        <v>-0.03900709219858156</v>
       </c>
       <c r="AB5">
-        <v>0.05067212097004738</v>
+        <v>0.09114418822594032</v>
       </c>
       <c r="AC5">
-        <v>0.05891839956783684</v>
+        <v>-0.1301512804245219</v>
       </c>
       <c r="AD5">
-        <v>13.4</v>
+        <v>29.8</v>
       </c>
       <c r="AE5">
-        <v>0.01459757425615745</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>13.41459757425616</v>
+        <v>29.8</v>
       </c>
       <c r="AG5">
-        <v>-11.78540242574384</v>
+        <v>14.8</v>
       </c>
       <c r="AH5">
-        <v>0.05167119915288759</v>
+        <v>0.3762626262626262</v>
       </c>
       <c r="AI5">
-        <v>0.05490706534708377</v>
+        <v>0.3193997856377278</v>
       </c>
       <c r="AJ5">
-        <v>-0.05027588958921617</v>
+        <v>0.2305295950155763</v>
       </c>
       <c r="AK5">
-        <v>-0.05378647774368325</v>
+        <v>0.1890166028097063</v>
       </c>
       <c r="AL5">
-        <v>0.979</v>
+        <v>1.01</v>
       </c>
       <c r="AM5">
-        <v>0.979</v>
+        <v>1.01</v>
       </c>
       <c r="AN5">
-        <v>0.5951587830335332</v>
+        <v>113.7404580152672</v>
       </c>
       <c r="AO5">
-        <v>22.16547497446374</v>
+        <v>-2.178217821782178</v>
       </c>
       <c r="AP5">
-        <v>-0.5234466989004593</v>
+        <v>56.48854961832061</v>
       </c>
       <c r="AQ5">
-        <v>22.16547497446374</v>
+        <v>-2.178217821782178</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai Islamic Insurance &amp; Reinsurance Co. (Aman) (P.J.S.C) (DFM:AMAN)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>-0.0266</v>
+      </c>
+      <c r="G6">
+        <v>0.07106598984771574</v>
+      </c>
+      <c r="H6">
+        <v>0.07106598984771574</v>
+      </c>
+      <c r="I6">
+        <v>-0.09644670050761421</v>
+      </c>
+      <c r="J6">
+        <v>-0.09644670050761421</v>
+      </c>
+      <c r="K6">
+        <v>-3.22</v>
+      </c>
+      <c r="L6">
+        <v>-0.08172588832487311</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>29</v>
+      </c>
+      <c r="V6">
+        <v>0.5360443622920518</v>
+      </c>
+      <c r="W6">
+        <v>-0.1364406779661017</v>
+      </c>
+      <c r="X6">
+        <v>0.08567336415958873</v>
+      </c>
+      <c r="Y6">
+        <v>-0.2221140421256904</v>
+      </c>
+      <c r="Z6">
+        <v>3.92430278884462</v>
+      </c>
+      <c r="AA6">
+        <v>-0.3784860557768923</v>
+      </c>
+      <c r="AB6">
+        <v>0.08567336415958873</v>
+      </c>
+      <c r="AC6">
+        <v>-0.464159419936481</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>-29</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>-1.155378486055777</v>
+      </c>
+      <c r="AK6">
+        <v>5.087719298245615</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>-0</v>
+      </c>
+      <c r="AP6">
+        <v>7.692307692307693</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_insurance_prop_cas.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.01245</v>
+        <v>0.03456</v>
       </c>
       <c r="E2">
-        <v>-0.178</v>
+        <v>-0.13</v>
       </c>
       <c r="G2">
-        <v>0.07536332179930796</v>
+        <v>0.01501535127325266</v>
       </c>
       <c r="H2">
-        <v>0.07536332179930796</v>
+        <v>0.01501535127325266</v>
       </c>
       <c r="I2">
-        <v>0.006412217440843681</v>
+        <v>0.01007260266620388</v>
       </c>
       <c r="J2">
-        <v>0.006079275381415259</v>
+        <v>0.009337418448613138</v>
       </c>
       <c r="K2">
-        <v>-4.696</v>
+        <v>-11.48</v>
       </c>
       <c r="L2">
-        <v>-0.01083275663206459</v>
+        <v>-0.02073324905183313</v>
       </c>
       <c r="M2">
-        <v>10.08</v>
+        <v>0.665</v>
       </c>
       <c r="N2">
-        <v>0.02868525896414343</v>
+        <v>0.002824978759558199</v>
       </c>
       <c r="O2">
-        <v>-2.146507666098808</v>
+        <v>-0.05792682926829269</v>
       </c>
       <c r="P2">
-        <v>10.08</v>
+        <v>0.337</v>
       </c>
       <c r="Q2">
-        <v>0.02868525896414343</v>
+        <v>0.00143160577740017</v>
       </c>
       <c r="R2">
-        <v>-2.146507666098808</v>
+        <v>-0.02935540069686411</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.328</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.4932330827067669</v>
       </c>
       <c r="U2">
-        <v>100.75</v>
+        <v>66.28</v>
       </c>
       <c r="V2">
-        <v>0.2867103016505407</v>
+        <v>0.2815632965165676</v>
       </c>
       <c r="W2">
-        <v>-0.07258523505695386</v>
+        <v>-0.04240694834646248</v>
       </c>
       <c r="X2">
-        <v>0.08803084284500959</v>
+        <v>0.07409423482750793</v>
       </c>
       <c r="Y2">
-        <v>-0.1606160779019634</v>
+        <v>-0.1165011831739704</v>
       </c>
       <c r="Z2">
-        <v>1.239398218031192</v>
+        <v>3.138995666015096</v>
       </c>
       <c r="AA2">
-        <v>-0.0261756277887779</v>
+        <v>-0.06067124991710954</v>
       </c>
       <c r="AB2">
-        <v>0.08681079478660299</v>
+        <v>0.07388692328052859</v>
       </c>
       <c r="AC2">
-        <v>-0.1156205832046331</v>
+        <v>-0.1345581731976381</v>
       </c>
       <c r="AD2">
-        <v>38.76</v>
+        <v>23.677</v>
       </c>
       <c r="AE2">
-        <v>0.04651869697132015</v>
+        <v>0.7139995186145492</v>
       </c>
       <c r="AF2">
-        <v>38.80651869697132</v>
+        <v>24.39099951861455</v>
       </c>
       <c r="AG2">
-        <v>-61.94348130302868</v>
+        <v>-41.88900048138545</v>
       </c>
       <c r="AH2">
-        <v>0.09945123117512011</v>
+        <v>0.0938870074937561</v>
       </c>
       <c r="AI2">
-        <v>0.09041456037243817</v>
+        <v>0.07195176141328556</v>
       </c>
       <c r="AJ2">
-        <v>-0.213999261726341</v>
+        <v>-0.2164683174888774</v>
       </c>
       <c r="AK2">
-        <v>-0.188589593376823</v>
+        <v>-0.1536021669654957</v>
       </c>
       <c r="AL2">
-        <v>1.62</v>
+        <v>2.077</v>
       </c>
       <c r="AM2">
-        <v>1.62</v>
+        <v>2.077</v>
       </c>
       <c r="AN2">
-        <v>5.010989010989012</v>
+        <v>1.955161023947151</v>
       </c>
       <c r="AO2">
-        <v>1.691358024691359</v>
+        <v>2.392874337987482</v>
       </c>
       <c r="AP2">
-        <v>-8.008207020430341</v>
+        <v>-3.459042153706478</v>
       </c>
       <c r="AQ2">
-        <v>1.691358024691359</v>
+        <v>2.392874337987482</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Islamic Arab Insurance Co. (Salama) PJSC (DFM:SALAMA)</t>
+          <t>Dubai Islamic Insurance &amp; Reinsurance Co. (Aman) (P.J.S.C) (DFM:AMAN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,121 +722,103 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.011</v>
+        <v>-0.0832</v>
       </c>
       <c r="E3">
-        <v>-0.178</v>
+        <v>-0.129</v>
       </c>
       <c r="G3">
-        <v>0.07951219512195122</v>
+        <v>-0.03384</v>
       </c>
       <c r="H3">
-        <v>0.07951219512195122</v>
+        <v>-0.03384</v>
       </c>
       <c r="I3">
-        <v>0.04843754273466213</v>
+        <v>0.1508</v>
       </c>
       <c r="J3">
-        <v>0.03837743770515538</v>
+        <v>0.1508</v>
       </c>
       <c r="K3">
-        <v>4.94</v>
+        <v>1.88</v>
       </c>
       <c r="L3">
-        <v>0.02409756097560976</v>
+        <v>0.07519999999999999</v>
       </c>
       <c r="M3">
-        <v>6.46</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.03760186263096624</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>1.307692307692307</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>6.46</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.03760186263096624</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>1.307692307692307</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>48.3</v>
+        <v>7.99</v>
       </c>
       <c r="V3">
-        <v>0.2811408614668218</v>
+        <v>0.299250936329588</v>
       </c>
       <c r="W3">
-        <v>0.02364767831498325</v>
+        <v>0.07932489451476793</v>
       </c>
       <c r="X3">
-        <v>0.08633540778312301</v>
+        <v>0.07394252064490406</v>
       </c>
       <c r="Y3">
-        <v>-0.06268772946813977</v>
-      </c>
-      <c r="Z3">
-        <v>1.039835759489621</v>
-      </c>
-      <c r="AA3">
-        <v>0.03990623208340587</v>
+        <v>0.005382373869863871</v>
       </c>
       <c r="AB3">
-        <v>0.08587586696743588</v>
-      </c>
-      <c r="AC3">
-        <v>-0.04596963488403001</v>
+        <v>0.07394252064490406</v>
       </c>
       <c r="AD3">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>0.04651869697132015</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.42651869697132</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-45.87348130302868</v>
+        <v>-7.99</v>
       </c>
       <c r="AH3">
-        <v>0.0139273786511898</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.01078805074220887</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.3642876955363015</v>
+        <v>-0.4270443613041154</v>
       </c>
       <c r="AK3">
-        <v>-0.2597202370371765</v>
+        <v>-0.4781567923399162</v>
       </c>
       <c r="AL3">
-        <v>0.5679999999999999</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.5679999999999999</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.2214159456693646</v>
-      </c>
-      <c r="AO3">
-        <v>17.41197183098592</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>-4.267697581452105</v>
-      </c>
-      <c r="AQ3">
-        <v>17.41197183098592</v>
+        <v>-2.102631578947368</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Al Fujairah National Insurance Company P.J.S.C (ADX:AFNIC)</t>
+          <t>Islamic Arab Insurance Co. (Salama) PJSC (DFM:SALAMA)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,118 +838,118 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0139</v>
+        <v>0.0733</v>
+      </c>
+      <c r="E4">
+        <v>-0.131</v>
       </c>
       <c r="G4">
-        <v>0.1106589147286822</v>
+        <v>0.05080313784086665</v>
       </c>
       <c r="H4">
-        <v>0.1106589147286822</v>
+        <v>0.05080313784086665</v>
       </c>
       <c r="I4">
-        <v>-0.02228682170542635</v>
+        <v>0.06577213334432981</v>
       </c>
       <c r="J4">
-        <v>-0.02228682170542635</v>
+        <v>0.04656969441391628</v>
       </c>
       <c r="K4">
-        <v>-0.756</v>
+        <v>6.35</v>
       </c>
       <c r="L4">
-        <v>-0.01465116279069767</v>
+        <v>0.02372058274187523</v>
       </c>
       <c r="M4">
-        <v>3.62</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.04756898817345599</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>-4.788359788359789</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>3.62</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.04756898817345599</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>-4.788359788359789</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>8.449999999999999</v>
+        <v>29</v>
       </c>
       <c r="V4">
-        <v>0.1110381077529566</v>
+        <v>0.2098408104196816</v>
       </c>
       <c r="W4">
-        <v>-0.008729792147806005</v>
+        <v>0.03148239960337134</v>
       </c>
       <c r="X4">
-        <v>0.08972627790689615</v>
+        <v>0.07424594901011181</v>
       </c>
       <c r="Y4">
-        <v>-0.09845607005470215</v>
+        <v>-0.04276354940674047</v>
       </c>
       <c r="Z4">
-        <v>0.5987468090044095</v>
+        <v>1.710608718695044</v>
       </c>
       <c r="AA4">
-        <v>-0.01334416337897424</v>
+        <v>0.07966252529140906</v>
       </c>
       <c r="AB4">
-        <v>0.0877457226057701</v>
+        <v>0.07383132591615313</v>
       </c>
       <c r="AC4">
-        <v>-0.1010898859847443</v>
+        <v>0.005831199375255933</v>
       </c>
       <c r="AD4">
-        <v>6.58</v>
+        <v>0.877</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>0.7139995186145492</v>
       </c>
       <c r="AF4">
-        <v>6.58</v>
+        <v>1.590999518614549</v>
       </c>
       <c r="AG4">
-        <v>-1.869999999999999</v>
+        <v>-27.40900048138545</v>
       </c>
       <c r="AH4">
-        <v>0.07958393807450412</v>
+        <v>0.01138127292954002</v>
       </c>
       <c r="AI4">
-        <v>0.07504562043795621</v>
+        <v>0.007160503900074762</v>
       </c>
       <c r="AJ4">
-        <v>-0.02519197090125285</v>
+        <v>-0.2473937467887933</v>
       </c>
       <c r="AK4">
-        <v>-0.02360217089486305</v>
+        <v>-0.1418751419563131</v>
       </c>
       <c r="AL4">
-        <v>0.042</v>
+        <v>0.927</v>
       </c>
       <c r="AM4">
-        <v>0.042</v>
+        <v>0.927</v>
       </c>
       <c r="AN4">
-        <v>13.31983805668016</v>
+        <v>0.04702412868632708</v>
       </c>
       <c r="AO4">
-        <v>-27.38095238095238</v>
+        <v>18.33872707659115</v>
       </c>
       <c r="AP4">
-        <v>-3.785425101214573</v>
+        <v>-1.469651500342384</v>
       </c>
       <c r="AQ4">
-        <v>-27.38095238095238</v>
+        <v>18.33872707659115</v>
       </c>
     </row>
     <row r="5">
@@ -978,7 +960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dar Al Takaful PJSC (DFM:DARTAKAFUL)</t>
+          <t>Insurance House P.S.C. (ADX:IH)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -987,115 +969,112 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.213</v>
+        <v>-0.00418</v>
       </c>
       <c r="G5">
-        <v>0.05716363636363637</v>
+        <v>0.05055679287305122</v>
       </c>
       <c r="H5">
-        <v>0.05716363636363637</v>
+        <v>0.05055679287305122</v>
       </c>
       <c r="I5">
-        <v>-0.016</v>
+        <v>-0.08908685968819599</v>
       </c>
       <c r="J5">
-        <v>-0.016</v>
+        <v>-0.08908685968819599</v>
       </c>
       <c r="K5">
-        <v>-5.66</v>
+        <v>-4.71</v>
       </c>
       <c r="L5">
-        <v>-0.04116363636363637</v>
+        <v>-0.1048997772828508</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>0.665</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.0240072202166065</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-0.1411889596602972</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>0.337</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.01216606498194946</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>-0.07154989384288749</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>0.328</v>
+      </c>
+      <c r="T5">
+        <v>0.4932330827067669</v>
       </c>
       <c r="U5">
-        <v>15</v>
+        <v>4.19</v>
       </c>
       <c r="V5">
-        <v>0.3036437246963563</v>
+        <v>0.1512635379061372</v>
       </c>
       <c r="W5">
-        <v>-0.1422110552763819</v>
+        <v>-0.1162962962962963</v>
       </c>
       <c r="X5">
-        <v>0.1139491992194216</v>
+        <v>0.07394252064490406</v>
       </c>
       <c r="Y5">
-        <v>-0.2561602544958035</v>
+        <v>-0.1902388169412004</v>
       </c>
       <c r="Z5">
-        <v>2.437943262411348</v>
+        <v>2.256281407035176</v>
       </c>
       <c r="AA5">
-        <v>-0.03900709219858156</v>
+        <v>-0.2010050251256282</v>
       </c>
       <c r="AB5">
-        <v>0.09114418822594032</v>
+        <v>0.07394252064490406</v>
       </c>
       <c r="AC5">
-        <v>-0.1301512804245219</v>
+        <v>-0.2749475457705322</v>
       </c>
       <c r="AD5">
-        <v>29.8</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>29.8</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>14.8</v>
+        <v>-4.19</v>
       </c>
       <c r="AH5">
-        <v>0.3762626262626262</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.3193997856377278</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>0.2305295950155763</v>
+        <v>-0.1782220331773714</v>
       </c>
       <c r="AK5">
-        <v>0.1890166028097063</v>
+        <v>-0.6152716593245229</v>
       </c>
       <c r="AL5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>113.7404580152672</v>
-      </c>
-      <c r="AO5">
-        <v>-2.178217821782178</v>
+        <v>-0</v>
       </c>
       <c r="AP5">
-        <v>56.48854961832061</v>
-      </c>
-      <c r="AQ5">
-        <v>-2.178217821782178</v>
+        <v>1.154269972451791</v>
       </c>
     </row>
     <row r="6">
@@ -1106,7 +1085,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dubai Islamic Insurance &amp; Reinsurance Co. (Aman) (P.J.S.C) (DFM:AMAN)</t>
+          <t>Watania International Holding PJSC (DFM:WATANIA)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1115,25 +1094,25 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0266</v>
+        <v>0.311</v>
       </c>
       <c r="G6">
-        <v>0.07106598984771574</v>
+        <v>-0.03105043961129107</v>
       </c>
       <c r="H6">
-        <v>0.07106598984771574</v>
+        <v>-0.03105043961129107</v>
       </c>
       <c r="I6">
-        <v>-0.09644670050761421</v>
+        <v>-0.05460434983803795</v>
       </c>
       <c r="J6">
-        <v>-0.09644670050761421</v>
+        <v>-0.05460434983803795</v>
       </c>
       <c r="K6">
-        <v>-3.22</v>
+        <v>-15</v>
       </c>
       <c r="L6">
-        <v>-0.08172588832487311</v>
+        <v>-0.06941230911614993</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1157,67 +1136,58 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>29</v>
+        <v>25.1</v>
       </c>
       <c r="V6">
-        <v>0.5360443622920518</v>
-      </c>
-      <c r="W6">
-        <v>-0.1364406779661017</v>
+        <v>0.5864485981308412</v>
       </c>
       <c r="X6">
-        <v>0.08567336415958873</v>
-      </c>
-      <c r="Y6">
-        <v>-0.2221140421256904</v>
-      </c>
-      <c r="Z6">
-        <v>3.92430278884462</v>
-      </c>
-      <c r="AA6">
-        <v>-0.3784860557768923</v>
+        <v>0.08798310716424658</v>
       </c>
       <c r="AB6">
-        <v>0.08567336415958873</v>
-      </c>
-      <c r="AC6">
-        <v>-0.464159419936481</v>
+        <v>0.07206187760457096</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>22.8</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>22.8</v>
       </c>
       <c r="AG6">
-        <v>-29</v>
+        <v>-2.300000000000001</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.3475609756097561</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.281134401972873</v>
       </c>
       <c r="AJ6">
-        <v>-1.155378486055777</v>
+        <v>-0.05679012345679014</v>
       </c>
       <c r="AK6">
-        <v>5.087719298245615</v>
+        <v>-0.04107142857142859</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN6">
-        <v>-0</v>
+        <v>-3.397913561847988</v>
+      </c>
+      <c r="AO6">
+        <v>-10.26086956521739</v>
       </c>
       <c r="AP6">
-        <v>7.692307692307693</v>
+        <v>0.3427719821162445</v>
+      </c>
+      <c r="AQ6">
+        <v>-10.26086956521739</v>
       </c>
     </row>
   </sheetData>
